--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="D2">
-        <v>141</v>
+        <v>294</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="D3">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D3">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
